--- a/artfynd/A 27910-2024 artfynd.xlsx
+++ b/artfynd/A 27910-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95511129</v>
+        <v>95511151</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597509.8375596473</v>
+        <v>597466</v>
       </c>
       <c r="R2" t="n">
-        <v>7014314.948468056</v>
+        <v>7014358</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95511117</v>
+        <v>95511120</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597487.0197433969</v>
+        <v>597487</v>
       </c>
       <c r="R3" t="n">
-        <v>7014248.432781341</v>
+        <v>7014249</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +847,9 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +880,7 @@
         <v>95511128</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,12 +897,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597509.8375596473</v>
+        <v>597510</v>
       </c>
       <c r="R4" t="n">
-        <v>7014314.948468056</v>
+        <v>7014315</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,19 +948,9 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,12 +981,7 @@
         <v>95511138</v>
       </c>
       <c r="B5" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,12 +998,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597475.6008106592</v>
+        <v>597476</v>
       </c>
       <c r="R5" t="n">
-        <v>7014342.315853096</v>
+        <v>7014343</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,19 +1049,9 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95511124</v>
+        <v>95511146</v>
       </c>
       <c r="B6" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597487.0197433969</v>
+        <v>597466</v>
       </c>
       <c r="R6" t="n">
-        <v>7014248.432781341</v>
+        <v>7014358</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1215,19 +1150,9 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95511120</v>
+        <v>105158048</v>
       </c>
       <c r="B7" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,28 +1200,25 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nordsjö, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597487.0197433969</v>
+        <v>597431</v>
       </c>
       <c r="R7" t="n">
-        <v>7014248.432781341</v>
+        <v>7014186</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,22 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,34 +1259,32 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105158052</v>
+        <v>105158050</v>
       </c>
       <c r="B8" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,12 +1301,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597368.5360848723</v>
+        <v>597363</v>
       </c>
       <c r="R8" t="n">
-        <v>7014210.13293327</v>
+        <v>7014197</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,19 +1349,9 @@
           <t>2022-07-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105158047</v>
+        <v>105158052</v>
       </c>
       <c r="B9" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597517.6576189777</v>
+        <v>597368</v>
       </c>
       <c r="R9" t="n">
-        <v>7014339.981968872</v>
+        <v>7014210</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,19 +1450,9 @@
           <t>2022-07-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105158048</v>
+        <v>95511117</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,34 +1494,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Nordsjö, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597430.6716535424</v>
+        <v>597487</v>
       </c>
       <c r="R10" t="n">
-        <v>7014185.861259148</v>
+        <v>7014249</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1673,22 +1551,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,72 +1565,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Lena Högberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105158051</v>
+        <v>95511129</v>
       </c>
       <c r="B11" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Nordsjö, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597373.5369392066</v>
+        <v>597510</v>
       </c>
       <c r="R11" t="n">
-        <v>7014194.052890451</v>
+        <v>7014315</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1789,22 +1652,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,37 +1666,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Lena Högberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Lena Högberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105158050</v>
+        <v>95511148</v>
       </c>
       <c r="B12" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,34 +1696,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Nordsjö, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597363.5180665941</v>
+        <v>597466</v>
       </c>
       <c r="R12" t="n">
-        <v>7014196.906144352</v>
+        <v>7014358</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1905,22 +1753,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,21 +1767,321 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Lena Högberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lena Högberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>105158047</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>597518</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7014340</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Långsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Jennifer C. Johansson</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>95511124</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nordsjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>597487</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7014249</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Långsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lena Högberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lena Högberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105158051</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>597374</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7014194</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Långsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-07-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>

--- a/artfynd/A 27910-2024 artfynd.xlsx
+++ b/artfynd/A 27910-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95511151</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95511120</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95511128</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95511138</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95511146</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105158048</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105158050</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105158052</t>
         </is>
       </c>
     </row>
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95511117</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95511129</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95511148</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1882,6 +1942,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105158047</t>
         </is>
       </c>
     </row>
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95511124</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,8 +2156,29 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105158051</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>